--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlMufeedM\Desktop\Supplier Regisstration\Mivors-Maaden-Validate Supplier Registeration request LIVE\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Mivors\New folder\Mivors-Maaden-Validate-Supplier-Registeration-request\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27B1804-361A-4EEE-8E83-BB796AC69723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="7350" activeTab="5"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="116">
   <si>
     <t>Name</t>
   </si>
@@ -243,9 +244,6 @@
     <t>Manufacturer</t>
   </si>
   <si>
-    <t>Manufacturer Questioneries</t>
-  </si>
-  <si>
     <t>Project Contractor</t>
   </si>
   <si>
@@ -253,9 +251,6 @@
   </si>
   <si>
     <t>Training</t>
-  </si>
-  <si>
-    <t>Training Questions</t>
   </si>
   <si>
     <t>SMEs Remote Areas</t>
@@ -374,9 +369,6 @@
     <t>An official certificate or business registration document issued by a recognized government authority or ministry of commerce in any country, confirming that a business is legally registered and authorized to operate. In Saudi Arabia, it is issued by the Ministry of Commerce (وزارة التجارة). Internationally, equivalent documents may be issued by Companies House (UK), SEC or State authorities (USA), ACRA (Singapore), MCA (India), or similar national registries worldwide. The document contains the company's legal name, a unique registration/CR number, the type of commercial activity or business nature, and registration/expiry or renewal details. It may be printed in Arabic, English, or any other official language of the issuing country. Key labels to look for (Arabic): "السجل التجاري"," الرقم الوطني الموحد  , "رقم السجل التجاري", "تاريخ الانتهاء", "اسم المنشأة", "النشاط التجاري". Key labels to look for (English): "Commercial Registration", "Business Registration Certificate", "Certificate of Incorporation", "Company Registration Number", "CRN", "Registration Number", "Registered Name", "Expiry Date", "Valid Until", "Date of Incorporation","the unified national number for example 7050299762 ". Key labels to look for (other): Any equivalent terms in the document's local language that indicate official business registration, company identity, and validity period. Dates may appear in Hijri (e.g. ١٤٤٦/٠٥/١٢ or 1446/05/12), Gregorian (DD/MM/YYYY or MM/DD/YYYY or YYYY-MM-DD), or any locally used calendar format. Always convert to Gregorian DD/MM/YYYY. Note: If no expiry date is present (e.g. some countries issue lifetime registrations), return "" for expiration_date.</t>
   </si>
   <si>
-    <t>An official letter issued by a licensed bank confirming the IBAN (International Bank Account Number) assigned to a specific account holder or  not an official bank-issued IBAN confirmation letter but countain Valiad IBAN and Bank account. In Saudi Arabia, it is issued by Saudi-licensed banks such as Al Rajhi Bank, SNB, Riyad Bank, or SAB. Internationally, equivalent letters may be issued by any licensed bank worldwide. The document is typically issued on official bank letterhead and includes the bank's name, the account holder's name, the IBAN number, and the basic bank account number. Key labels to look for (Arabic): "خطاب تأكيد الآيبان", "اسم البنك", "رقم الآيبان", "رقم الحساب", "اسم صاحب الحساب". Key labels to look for (English): "IBAN Confirmation Letter", "Bank Name", "IBAN", "Account Number", "Account Holder Name", "International Bank Account Number". Key labels to look for (other): Any equivalent terms in the document's local language that indicate official bank confirmation, IBAN number, and account details. Saudi IBAN always starts with "SA" followed by 22 digits (total 24 characters). International IBANs start with a 2-letter country</t>
-  </si>
-  <si>
     <t>Please attach your Company Profile/Presentation</t>
   </si>
   <si>
@@ -399,12 +391,74 @@
   </si>
   <si>
     <t>Please upload the VAT Registration Certificate</t>
+  </si>
+  <si>
+    <t>An official bank-issued document that confirms the banking details of an account holder. This document is typically used for supplier registration and financial verification purposes.
+### **Scope**
+* **Saudi Arabia Suppliers:**
+  The document must be an **IBAN Confirmation Letter** issued by a **Saudi Arabia–licensed bank** (e.g., Al Rajhi Bank, SNB, Riyadh Bank, SAB).
+* **International / Non-Saudi Suppliers:**
+  The document may be issued by **any licensed bank** in the supplier’s country (`{{variable for Country}}`).
+  In such cases, **IBAN is optional**, and **Account Number is mandatory**.
+---
+### **Document Requirements**
+The document must:
+* Be issued on **official bank letterhead**
+* Clearly display the **bank’s identity**
+* Contain verified account details of the account holder
+---
+### **Required Data Fields (Extract &amp; Validate)**
+* **Bank Name**
+* **Account Holder Name**
+* **Account Number** (mandatory for all cases)
+* **IBAN**
+  * **Mandatory for Saudi suppliers**
+  * Optional for international suppliers
+---
+### **Validation Rules**
+* **Saudi IBAN Format:**
+  * Must start with **"SA"**
+  * Followed by **22 digits**
+  * Total length: **24 characters**
+* **International IBAN Format (if present):**
+  * Must start with a **2-letter country code**
+  * Follow standard IBAN structure (country-specific length and format)
+* The document must clearly indicate it is an **official bank-issued confirmation**
+---
+### **Key Labels / Keywords to Identify**
+**Arabic:**
+* "خطاب تأكيد الآيبان"
+* "اسم البنك"
+* "رقم الآيبان"
+* "رقم الحساب"
+* "اسم صاحب الحساب"
+**English:**
+* "IBAN Confirmation Letter"
+* "Bank Name"
+* "IBAN"
+* "Account Number"
+* "Account Holder Name"
+* "International Bank Account Number"
+**Other Languages:**
+* Any equivalent terminology indicating:
+  * Official bank confirmation
+  * IBAN or account number
+  * Account holder identity
+---
+### **Acceptance Criteria**
+A document is considered valid if:
+1. It is issued by a licensed bank
+2. It contains all required fields based on supplier type (Saudi vs International)
+3. The IBAN (if required/present) passes format validation
+4. The document clearly represents an official bank confirmation
+---
+If you want, I can also convert this into a **strict JSON schema for automated validation** or a **prompt optimized for OCR/AI extraction systems**.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -808,7 +862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z998"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -857,7 +911,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -868,7 +922,7 @@
         <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>32</v>
@@ -889,103 +943,103 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="B8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="B10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="B11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="B13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="B14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="B15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="B16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="14.25" customHeight="1">
       <c r="B17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="14.25" customHeight="1">
       <c r="B18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="14.25" customHeight="1">
       <c r="B19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="14.25" customHeight="1">
       <c r="B20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="14.25" customHeight="1"/>
     <row r="22" spans="2:2" ht="14.25" customHeight="1">
       <c r="B22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="14.25" customHeight="1">
       <c r="B23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="14.25" customHeight="1">
       <c r="B24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="14.25" customHeight="1">
       <c r="B25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="14.25" customHeight="1">
       <c r="B26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="14.25" customHeight="1">
       <c r="B27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="14.25" customHeight="1">
       <c r="B28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="14.25" customHeight="1"/>
@@ -1966,7 +2020,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -1976,10 +2030,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2002,65 +2056,66 @@
       <c r="A4" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>66</v>
+      <c r="B4" s="7" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -2086,10 +2141,10 @@
         <v>51</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2120,10 +2175,10 @@
         <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2140,10 +2195,10 @@
         <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2160,10 +2215,10 @@
         <v>55</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2191,7 +2246,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z988"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3356,7 +3411,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -3385,7 +3440,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3395,7 +3450,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -3404,31 +3459,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -3438,7 +3493,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
@@ -3449,7 +3504,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3459,7 +3514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
